--- a/reports/올리브영_시딩_성과보고서_HAN_260907.xlsx
+++ b/reports/올리브영_시딩_성과보고서_HAN_260907.xlsx
@@ -243,11 +243,11 @@
     <xf numFmtId="168" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -642,18 +642,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -750,11 +750,11 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>크리에이터 원고료</t>
+          <t>시딩 비용 확인분</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>494201000</v>
+        <v>524201000</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -776,11 +776,11 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>원고료 비중</t>
+          <t>청구액 대비 비중</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5822228462600613</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>5.3939</v>
+        <v>5.393784423623202</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -913,11 +913,11 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (구성) 크리에이터 원고료</t>
+          <t xml:space="preserve">  (구성) 시딩 비용 확인분</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>494201000</v>
+        <v>524201000</v>
       </c>
       <c r="C14" s="19" t="n"/>
       <c r="D14" s="19" t="n"/>
@@ -930,7 +930,10 @@
         <f>B14/$F$13</f>
         <v/>
       </c>
-      <c r="H14" s="19" t="n"/>
+      <c r="H14" s="21">
+        <f>B14/$B$13</f>
+        <v/>
+      </c>
       <c r="I14" s="19">
         <f>B14/$C$13</f>
         <v/>
@@ -939,12 +942,11 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (구성) 마크업·VAT·솔루션·지급대행 등</t>
-        </is>
-      </c>
-      <c r="B15" s="19">
-        <f>B13-B14</f>
-        <v/>
+          <t xml:space="preserve">      · 원고료 기준 (국내 + WM·CG JP)</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>491870000</v>
       </c>
       <c r="C15" s="19" t="n"/>
       <c r="D15" s="19" t="n"/>
@@ -952,163 +954,136 @@
       <c r="F15" s="19" t="n"/>
       <c r="G15" s="19" t="n"/>
       <c r="H15" s="21">
-        <f>B15/B13</f>
+        <f>B15/$B$13</f>
         <v/>
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t>비시딩 항목·성과 미집계 건 대응분 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+          <t>마크업·VAT 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      · 청구 기준 (BOH JP + BOH US)</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>32331000</v>
+      </c>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="21">
+        <f>B16/$B$13</f>
+        <v/>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>BOH JP 건당 333,000(마크업 포함) + BOH US 틱톡 30,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (구성) 그 외</t>
+        </is>
+      </c>
+      <c r="B17" s="19">
+        <f>B13-B14</f>
+        <v/>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="21">
+        <f>B17/$B$13</f>
+        <v/>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>마크업·VAT·솔루션·지급대행·비시딩 항목·성과 미집계 건 대응분</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>국가별  —  세금계산서 발행액 기준</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>국가</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>시딩 건수</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>비중</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>발행액</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>비중</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>건당</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>조회수</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>진행월</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>국내 (KR)</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C19" s="21">
-        <f>B19/$B$22</f>
-        <v/>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>828051764</v>
-      </c>
-      <c r="E19" s="21">
-        <f>D19/$D$22</f>
-        <v/>
-      </c>
-      <c r="F19" s="19">
-        <f>IFERROR(D19/B19,"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>52536293</v>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>25.04 ~ 26.09</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>총 발행액 − JP·US 명시 라인</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>일본 (JP)</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>99</v>
-      </c>
-      <c r="C20" s="21">
-        <f>B20/$B$22</f>
-        <v/>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>42292500</v>
-      </c>
-      <c r="E20" s="21">
-        <f>D20/$D$22</f>
-        <v/>
-      </c>
-      <c r="F20" s="19">
-        <f>IFERROR(D20/B20,"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>407439</v>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>26.06 ~ 26.09</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>세금계산서 WM 22,067,500 + CG 20,225,000</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>미국 (US)</t>
+          <t>국내 (KR)</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>68</v>
+        <v>1998</v>
       </c>
       <c r="C21" s="21">
-        <f>B21/$B$22</f>
+        <f>B21/$B$24</f>
         <v/>
       </c>
       <c r="D21" s="19" t="n">
-        <v>30000000</v>
+        <v>828051764</v>
       </c>
       <c r="E21" s="21">
-        <f>D21/$D$22</f>
+        <f>D21/$D$24</f>
         <v/>
       </c>
       <c r="F21" s="19">
@@ -1116,90 +1091,173 @@
         <v/>
       </c>
       <c r="G21" s="19" t="n">
+        <v>52536293</v>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>25.04 ~ 26.09</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>총 발행액 − JP·US 명시 라인</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>일본 (JP)</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="C22" s="21">
+        <f>B22/$B$24</f>
+        <v/>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>42292500</v>
+      </c>
+      <c r="E22" s="21">
+        <f>D22/$D$24</f>
+        <v/>
+      </c>
+      <c r="F22" s="19">
+        <f>IFERROR(D22/B22,"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>407439</v>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>26.06 ~ 26.09</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>세금계산서 WM 22,067,500 + CG 20,225,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>미국 (US)</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>68</v>
+      </c>
+      <c r="C23" s="21">
+        <f>B23/$B$24</f>
+        <v/>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="E23" s="21">
+        <f>D23/$D$24</f>
+        <v/>
+      </c>
+      <c r="F23" s="19">
+        <f>IFERROR(D23/B23,"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="19" t="n">
         <v>4739117</v>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>25.08</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>2025 시딩 정산 59,830,000원 내 틱톡 시딩분</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B22" s="15">
-        <f>SUM(B19:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="17">
-        <f>B22/$B$22</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
-        <f>SUM(D19:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="17">
-        <f>D22/$D$22</f>
-        <v/>
-      </c>
-      <c r="F22" s="15">
-        <f>IFERROR(D22/B22,"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="15">
-        <f>SUM(G19:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
+      <c r="B24" s="15">
+        <f>SUM(B21:B23)</f>
+        <v/>
+      </c>
+      <c r="C24" s="17">
+        <f>B24/$B$24</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>SUM(D21:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>D24/$D$24</f>
+        <v/>
+      </c>
+      <c r="F24" s="15">
+        <f>IFERROR(D24/B24,"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="15">
+        <f>SUM(G21:G23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>25.04 ~ 26.09</t>
         </is>
       </c>
-      <c r="I22" s="25" t="inlineStr">
+      <c r="I24" s="25" t="inlineStr">
         <is>
           <t>조회수는 IMD 국가 태그 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>[팩트 원칙] 이 보고서의 모든 수치는 원천 자료 기재값이다. 추정·안분·보정값은 사용하지 않았다 (05_기준정의 참조).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>[모수] 수량·비용 = 전체 2,165건 / 조회수·참여 = IMD 성과 집계분 2,112건 · 미집계 53건(US 32 + JP 26.09 21)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>[참여수] 실측 좋아요 359,877 + 댓글 32,083 = 391,960. 좋아요 데이터가 없는 519건(조회수 8,976,727)은 추정하지 않았다 → 실제 참여는 이 값 이상 (A4-3)</t>
+          <t>[팩트 원칙] 모든 수치는 원천 자료 기재값이다. 추정·안분·보정값은 사용하지 않았다 (05_기준정의 ②).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>[금액] 세금계산서 발행 900,344,264원 = 26.02~08 확정 840,514,264 + 25년 발행 59,830,000(바이오힐보 US 30,000,000 포함). + JP 미발행 8,715,000 → 진행 기준 909,059,264</t>
+          <t>[모수] 수량·비용 = 전체 2,165건 / 조회수·참여 = IMD 성과 집계분 2,112건 · 미집계 53건(US 32 + JP 26.09 21)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>[참여수] 실측 좋아요 359,877 + 댓글 32,083 = 391,960. 좋아요 데이터가 없는 519건(조회수 8,976,727)은 추정하지 않았다 → 실제 참여·ER은 이 값 이상 (A4-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>[금액] 세금계산서 발행 900,344,264원 = 26.02~08 확정 840,514,264 + 2025 시딩 정산 59,830,000. + JP 미발행 8,715,000 → 진행 기준 909,059,264</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>[시딩 비용] 확인분 524,201,000원 = 원고료 기준 491,870,000 + 청구 기준 32,331,000. 기준이 다른 값이 섞여 있어 02_브랜드별 기준 열에 건별 표기했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>[상세] 브랜드별 → 02 · 연월별 → 03 · 광고 성과 → 04 · 산정 기준 → 05 · 원자료 → A1~A4</t>
         </is>
@@ -1223,10 +1281,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -1236,25 +1294,26 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>브랜드별 시딩 · 원고료 · 성과</t>
+          <t>브랜드별 시딩 · 비용 · 성과</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>팩트 집계 · 수량은 라인 자료, 원고료는 IMD 행 단위(국내) + JP 확정 단가, 성과는 IMD 실측</t>
+          <t>팩트 집계 · 수량은 라인 자료, 성과는 IMD 실측, 비용은 원고료/청구 기준을 열에 표기</t>
         </is>
       </c>
     </row>
@@ -1279,18 +1338,19 @@
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="28" t="inlineStr">
         <is>
-          <t>원고료</t>
+          <t>시딩 비용</t>
         </is>
       </c>
       <c r="L4" s="27" t="n"/>
-      <c r="M4" s="28" t="inlineStr">
+      <c r="M4" s="27" t="n"/>
+      <c r="N4" s="28" t="inlineStr">
         <is>
           <t>퍼포먼스 광고</t>
         </is>
       </c>
-      <c r="N4" s="27" t="n"/>
       <c r="O4" s="27" t="n"/>
       <c r="P4" s="27" t="n"/>
+      <c r="Q4" s="27" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
@@ -1346,30 +1406,35 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>원고료</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>광고비</t>
         </is>
       </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>전환 매출</t>
         </is>
       </c>
-      <c r="O5" s="13" t="inlineStr">
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1413,21 +1478,26 @@
       <c r="K6" s="19" t="n">
         <v>186700000</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M6" s="29">
         <f>K6/F6</f>
         <v/>
       </c>
-      <c r="M6" s="19" t="n">
+      <c r="N6" s="19" t="n">
         <v>33768439</v>
       </c>
-      <c r="N6" s="19" t="n">
+      <c r="O6" s="19" t="n">
         <v>102736712</v>
       </c>
-      <c r="O6" s="30">
-        <f>N6/M6</f>
-        <v/>
-      </c>
-      <c r="P6" s="22" t="inlineStr"/>
+      <c r="P6" s="30">
+        <f>O6/N6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
@@ -1467,21 +1537,26 @@
       <c r="K7" s="19" t="n">
         <v>66300000</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M7" s="29">
         <f>K7/F7</f>
         <v/>
       </c>
-      <c r="M7" s="19" t="n">
+      <c r="N7" s="19" t="n">
         <v>124304394</v>
       </c>
-      <c r="N7" s="19" t="n">
+      <c r="O7" s="19" t="n">
         <v>729266288</v>
       </c>
-      <c r="O7" s="30">
-        <f>N7/M7</f>
-        <v/>
-      </c>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="P7" s="30">
+        <f>O7/N7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>전체 광고비 44% · 매출 49%</t>
         </is>
@@ -1525,21 +1600,26 @@
       <c r="K8" s="19" t="n">
         <v>61550000</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M8" s="29">
         <f>K8/F8</f>
         <v/>
       </c>
-      <c r="M8" s="19" t="n">
+      <c r="N8" s="19" t="n">
         <v>133848</v>
       </c>
-      <c r="N8" s="19" t="n">
+      <c r="O8" s="19" t="n">
         <v>348140</v>
       </c>
-      <c r="O8" s="30">
-        <f>N8/M8</f>
-        <v/>
-      </c>
-      <c r="P8" s="22" t="inlineStr">
+      <c r="P8" s="30">
+        <f>O8/N8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
         <is>
           <t>ER 1위 · 광고는 1건만 집행</t>
         </is>
@@ -1583,21 +1663,26 @@
       <c r="K9" s="19" t="n">
         <v>37900000</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M9" s="29">
         <f>K9/F9</f>
         <v/>
       </c>
-      <c r="M9" s="19" t="n">
+      <c r="N9" s="19" t="n">
         <v>56333229</v>
       </c>
-      <c r="N9" s="19" t="n">
+      <c r="O9" s="19" t="n">
         <v>172219558</v>
       </c>
-      <c r="O9" s="30">
-        <f>N9/M9</f>
-        <v/>
-      </c>
-      <c r="P9" s="22" t="inlineStr"/>
+      <c r="P9" s="30">
+        <f>O9/N9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="inlineStr">
@@ -1637,22 +1722,27 @@
       <c r="K10" s="32" t="n">
         <v>2331000</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="34" t="inlineStr">
+        <is>
+          <t>청구</t>
+        </is>
+      </c>
+      <c r="M10" s="35">
         <f>K10/F10</f>
         <v/>
-      </c>
-      <c r="M10" s="32" t="n">
-        <v>0</v>
       </c>
       <c r="N10" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="35" t="inlineStr">
+      <c r="O10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P10" s="36" t="inlineStr">
+      <c r="Q10" s="36" t="inlineStr">
         <is>
           <t>26.06 NAD 크림 · 건당 333,000(마크업 포함)</t>
         </is>
@@ -1693,26 +1783,32 @@
         <f>I11/F11</f>
         <v/>
       </c>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="35" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="n">
-        <v>0</v>
+      <c r="K11" s="32" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="L11" s="34" t="inlineStr">
+        <is>
+          <t>청구</t>
+        </is>
+      </c>
+      <c r="M11" s="35">
+        <f>K11/F11</f>
+        <v/>
       </c>
       <c r="N11" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="35" t="inlineStr">
+      <c r="O11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P11" s="36" t="inlineStr">
-        <is>
-          <t>68건 중 36건 성과 확보 · 원고료 데이터 없음</t>
+      <c r="Q11" s="36" t="inlineStr">
+        <is>
+          <t>틱톡 68건 · 2025 시딩 정산 59,830,000원 내</t>
         </is>
       </c>
     </row>
@@ -1754,21 +1850,26 @@
       <c r="K12" s="19" t="n">
         <v>32490000</v>
       </c>
-      <c r="L12" s="29">
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M12" s="29">
         <f>K12/F12</f>
         <v/>
       </c>
-      <c r="M12" s="19" t="n">
+      <c r="N12" s="19" t="n">
         <v>14985030</v>
       </c>
-      <c r="N12" s="19" t="n">
+      <c r="O12" s="19" t="n">
         <v>118255596</v>
       </c>
-      <c r="O12" s="30">
-        <f>N12/M12</f>
-        <v/>
-      </c>
-      <c r="P12" s="22" t="inlineStr"/>
+      <c r="P12" s="30">
+        <f>O12/N12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
@@ -1808,21 +1909,26 @@
       <c r="K13" s="32" t="n">
         <v>40750000</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="34" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M13" s="35">
         <f>K13/F13</f>
         <v/>
       </c>
-      <c r="M13" s="32" t="n">
+      <c r="N13" s="32" t="n">
         <v>16409851</v>
       </c>
-      <c r="N13" s="32" t="n">
+      <c r="O13" s="32" t="n">
         <v>113788050</v>
       </c>
-      <c r="O13" s="37">
-        <f>N13/M13</f>
-        <v/>
-      </c>
-      <c r="P13" s="36" t="inlineStr">
+      <c r="P13" s="37">
+        <f>O13/N13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="36" t="inlineStr">
         <is>
           <t>JP 60건 건당 415,000 · 21건 미발행</t>
         </is>
@@ -1866,22 +1972,27 @@
       <c r="K14" s="19" t="n">
         <v>22500000</v>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M14" s="29">
         <f>K14/F14</f>
         <v/>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>0</v>
       </c>
       <c r="N14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="23" t="inlineStr">
+      <c r="O14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P14" s="22" t="inlineStr">
+      <c r="Q14" s="22" t="inlineStr">
         <is>
           <t>광고 미집행</t>
         </is>
@@ -1925,21 +2036,26 @@
       <c r="K15" s="32" t="n">
         <v>31680000</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M15" s="35">
         <f>K15/F15</f>
         <v/>
       </c>
-      <c r="M15" s="32" t="n">
+      <c r="N15" s="32" t="n">
         <v>23514230</v>
       </c>
-      <c r="N15" s="32" t="n">
+      <c r="O15" s="32" t="n">
         <v>134432958</v>
       </c>
-      <c r="O15" s="37">
-        <f>N15/M15</f>
-        <v/>
-      </c>
-      <c r="P15" s="36" t="inlineStr">
+      <c r="P15" s="37">
+        <f>O15/N15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="36" t="inlineStr">
         <is>
           <t>JP 32건 건당 415,000</t>
         </is>
@@ -1983,22 +2099,27 @@
       <c r="K16" s="19" t="n">
         <v>3700000</v>
       </c>
-      <c r="L16" s="29">
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M16" s="29">
         <f>K16/F16</f>
         <v/>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>0</v>
       </c>
       <c r="N16" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="23" t="inlineStr">
+      <c r="O16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P16" s="22" t="inlineStr">
+      <c r="Q16" s="22" t="inlineStr">
         <is>
           <t>26.07 신규 · 광고 미집행</t>
         </is>
@@ -2042,21 +2163,26 @@
       <c r="K17" s="19" t="n">
         <v>6300000</v>
       </c>
-      <c r="L17" s="29">
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M17" s="29">
         <f>K17/F17</f>
         <v/>
       </c>
-      <c r="M17" s="19" t="n">
+      <c r="N17" s="19" t="n">
         <v>14086284</v>
       </c>
-      <c r="N17" s="19" t="n">
+      <c r="O17" s="19" t="n">
         <v>121998372</v>
       </c>
-      <c r="O17" s="30">
-        <f>N17/M17</f>
-        <v/>
-      </c>
-      <c r="P17" s="22" t="inlineStr">
+      <c r="P17" s="30">
+        <f>O17/N17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="22" t="inlineStr">
         <is>
           <t>ROAS 1위</t>
         </is>
@@ -2100,22 +2226,27 @@
       <c r="K18" s="19" t="n">
         <v>2000000</v>
       </c>
-      <c r="L18" s="29">
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M18" s="29">
         <f>K18/F18</f>
         <v/>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>0</v>
       </c>
       <c r="N18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="23" t="inlineStr">
+      <c r="O18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P18" s="22" t="inlineStr">
+      <c r="Q18" s="22" t="inlineStr">
         <is>
           <t>광고 미집행</t>
         </is>
@@ -2167,23 +2298,28 @@
         <f>SUM(K6:K18)</f>
         <v/>
       </c>
-      <c r="L19" s="38">
+      <c r="L19" s="24" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="M19" s="38">
         <f>K19/F19</f>
-        <v/>
-      </c>
-      <c r="M19" s="15">
-        <f>SUM(M6:M18)</f>
         <v/>
       </c>
       <c r="N19" s="15">
         <f>SUM(N6:N18)</f>
         <v/>
       </c>
-      <c r="O19" s="39">
-        <f>N19/M19</f>
-        <v/>
-      </c>
-      <c r="P19" s="25" t="inlineStr">
+      <c r="O19" s="15">
+        <f>SUM(O6:O18)</f>
+        <v/>
+      </c>
+      <c r="P19" s="39">
+        <f>O19/N19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="25" t="inlineStr">
         <is>
           <t>수량 2,165 / 성과 집계 2,112</t>
         </is>
@@ -2199,42 +2335,49 @@
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>· 원고료 = 국내는 IMD 행 단위 기재값, JP는 확정 단가(웨이크메이크·컬러그램 415,000 / 바이오힐보 333,000). 케어플러스는 시딩현황 기재값 3,700,000.</t>
+          <t>· 시딩 비용 기준 — [원고료] 마크업·VAT 제외. 국내는 IMD 행 단위 기재값, JP는 확정 단가 건당 415,000, 케어플러스는 시딩현황 3,700,000.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>· IMD의 JP 원고료 기재값은 라인 총액을 행마다 반복 기재한 값이라 사용하지 않았다 (A2 각주 · A4-10).</t>
+          <t>· 시딩 비용 기준 — [청구] 마크업 포함. 바이오힐보 JP 건당 333,000(7건 2,331,000) · 바이오힐보 US 틱톡 30,000,000(2025 시딩 정산 59,830,000원 내).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>· CPV = 원고료 ÷ 조회수. 브랜드별 세금계산서 귀속은 발행 내역에 브랜드 미귀속액이 있어 산출하지 않았다 (A1 참조). 전체 청구 기준 단가는 01_요약.</t>
+          <t>· 합계 524,201,000원 = 원고료 기준 491,870,000 + 청구 기준 32,331,000. 기준이 섞여 있어 소계 CPV 9.09원은 참고값이다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>· 참여는 실측값이다. 좋아요 데이터가 없는 519건은 추정하지 않았으므로 실제 ER은 표기값 이상이다 (A4-3).</t>
+          <t>· IMD의 JP 원고료 기재값은 라인 총액을 행마다 반복 기재한 값이라 사용하지 않았다 (A2 각주 · A4-10).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>· 바이오힐보 US 68건(틱톡)은 원고료 데이터가 없어 CPV를 산출하지 않았다. 청구 30,000,000원은 2025 시딩 정산 59,830,000원 내에 포함되어 총액에 반영돼 있다.</t>
+          <t>· 브랜드별 세금계산서 귀속은 발행 내역에 브랜드 미귀속액 70,431,189원이 있어 산출하지 않았다 (A1). 전체 청구 기준 단가는 01_요약.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>· 참여는 실측값이다. 좋아요 데이터가 없는 519건은 추정하지 않았으므로 실제 ER은 표기값 이상이다 (A4-3).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="K4:M4"/>
     <mergeCell ref="F4:J4"/>
     <mergeCell ref="B4:E4"/>
   </mergeCells>
@@ -2250,17 +2393,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2341,7 +2484,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>바이오힐보 US 68건 (성과 확보 36건분 조회수)</t>
+          <t>바이오힐보 US 틱톡 68건 (성과 확보 36건분 조회수)</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2828,7 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>WM JP 21건 미발행(8,715,000) + 컬러그램 국내 1건</t>
+          <t>WM JP 21건 미발행 + 컬러그램 국내 1건</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2852,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>2025년 시딩 전체 운영비 · 그중 바이오힐보 US 틱톡 30,000,000</t>
+          <t>2025 시딩 전체 운영비 · 그중 바이오힐보 US 틱톡 30,000,000</t>
         </is>
       </c>
     </row>
@@ -2767,6 +2910,13 @@
       <c r="A24" s="26" t="inlineStr">
         <is>
           <t>· 25.08 US 68건 중 32건, 26.09 JP 21건은 성과 데이터가 없다 (조회수·광고비·매출 공란).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>· 26.09 JP 21건은 세금계산서 미발행이다 (원고료 8,715,000 = 21건 × 415,000).</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2943,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3670,13 +3820,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3735,12 +3885,12 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>세금계산서 월별 확정 총액표(26.09.07) 840,514,264 + 2025 시딩 정산 59,830,000</t>
+          <t>월별 확정 총액표(26.09.07) 840,514,264 + 2025 시딩 정산 59,830,000</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>2025 시딩은 전량 59,830,000원 내에서 운영 · 그중 US 틱톡 30,000,000</t>
+          <t>2025 시딩은 전량 59,830,000원 내에서 운영 · 그중 BOH US 틱톡 30,000,000</t>
         </is>
       </c>
     </row>
@@ -3813,40 +3963,44 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>원고료 (국내)</t>
+          <t>시딩 비용 (원고료 기준)</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>453,690,000원</t>
+          <t>491,870,000원</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>IMD 행 단위 기재값 + 케어플러스 시딩현황 3,700,000</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr"/>
+          <t>IMD 행 단위 기재값 + JP 확정 단가 415,000 + 케어플러스 시딩현황 3,700,000</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>마크업·VAT 제외</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>원고료 (JP)</t>
+          <t>시딩 비용 (청구 기준)</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>40,511,000원</t>
+          <t>32,331,000원</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>확정 단가 — WM 60건·CG 32건 × 415,000 / BOH 7건 × 333,000</t>
+          <t>바이오힐보 JP 7건 × 333,000 = 2,331,000 / 바이오힐보 US 틱톡 30,000,000</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>BOH는 마크업 포함 단가</t>
+          <t>마크업 포함</t>
         </is>
       </c>
     </row>
@@ -3941,7 +4095,7 @@
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>브랜드별은 원고료 기준 CPV로 표기 (02_브랜드별)</t>
+          <t>브랜드별은 시딩 비용(원고료/청구) 기준 CPV로 표기</t>
         </is>
       </c>
     </row>
@@ -3958,12 +4112,12 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>US 68건의 원고료 기준 CPV 산출 불가</t>
+          <t>US 68건은 청구 기준으로만 표기된다</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>청구 30,000,000원은 2025 시딩 정산 내에 포함 · 총액에 반영</t>
+          <t>기준 열에 "청구"로 명시</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4265,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>2025 시딩 계약 + 바이오힐보 US</t>
+          <t>2025 시딩 정산 (국내 272 + US 68)</t>
         </is>
       </c>
       <c r="B28" s="19" t="n">
@@ -4236,17 +4390,17 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>CPV (원고료)</t>
+          <t>CPV (시딩 비용)</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>원고료 494,201,000 ÷ 조회수 57,682,849</t>
+          <t>시딩 비용 524,201,000 ÷ 조회수 57,682,849</t>
         </is>
       </c>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>8.57원</t>
+          <t>9.09원</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr"/>
@@ -4332,6 +4486,13 @@
     </row>
     <row r="46">
       <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>데이터 단일 원천 — reports/data.py (모든 산출물이 이 파일에서만 값을 읽는다 · 저장 전 21항목 자체 검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>개인정산 정보(주민등록번호·계좌·주소·연락처)는 원장 시트에만 있으며 본 보고서에는 포함하지 않음</t>
         </is>
@@ -7294,7 +7455,7 @@
           <t>해결</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>루테카 발행액 71,375,000</t>
         </is>
@@ -7317,7 +7478,7 @@
           <t>해결</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>케어플러스 원고료</t>
         </is>
@@ -7340,7 +7501,7 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>2025 시딩 정산 구조</t>
         </is>
@@ -7363,7 +7524,7 @@
           <t>해결</t>
         </is>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>바이오힐보 US 성과</t>
         </is>
